--- a/tests/testdata/excel/保護/ブック構成保護.xlsx
+++ b/tests/testdata/excel/保護/ブック構成保護.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBBB96B5-B3A9-41DA-BD02-64444654E54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="yOITOczVxxldw/w101KgGW9mUzLj3hpBSWNbu/J4WSIuEN8v3cTD2wvpjhVfh0e8xxBrKku9c6gTnlvq0iCpAg==" workbookSaltValue="IPoTFwVbD776n8v0gXigSA==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{040FDA01-51A2-4AE5-830A-260D46C2E19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="6PXLPrPY2zgv4HFS/ErkqZ+VYzEu5dFBTnHo9Pl3UiaeLDLdHWSMUSB3Lxb5Zr/sQUMCQGKIIOXAr8fTOa3GBQ==" workbookSaltValue="AmorF5K1d7ilD1cdLyJi9g==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{E5A8EB14-9AA9-491E-A761-8F963CA37C1C}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{BF0CCD3B-ED2B-41CA-B4B6-88D166FE3344}"/>
   </bookViews>
   <sheets>
     <sheet name="構成保護1" sheetId="1" r:id="rId1"/>
@@ -432,7 +432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C31FD9-757A-43E4-9BF7-61C65CE23DAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C928C4-C8BE-4867-A81D-8B74908EA04B}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -451,7 +451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DFA8BD9-C790-4299-AEF3-CD1937BDE02C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84AE7AFC-47DB-4C76-855D-56C3FA4C841F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/保護/ブック構成保護.xlsx
+++ b/tests/testdata/excel/保護/ブック構成保護.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{040FDA01-51A2-4AE5-830A-260D46C2E19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="6PXLPrPY2zgv4HFS/ErkqZ+VYzEu5dFBTnHo9Pl3UiaeLDLdHWSMUSB3Lxb5Zr/sQUMCQGKIIOXAr8fTOa3GBQ==" workbookSaltValue="AmorF5K1d7ilD1cdLyJi9g==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51C0F1E2-14B2-40AC-8E26-E3DA5E55A663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="v651K7TG6ZL8U8i8ROaLWKCpaMJ3yA8uiZVp1tbYQj8p1rZgSMb04VKXs298nEGREWZXsCosVVecdA4WZPKE1A==" workbookSaltValue="k/cMIwP72nQDgV1EFnFS/g==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{BF0CCD3B-ED2B-41CA-B4B6-88D166FE3344}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{FB972546-3D05-4EB5-BE6C-9CD15C2689A4}"/>
   </bookViews>
   <sheets>
     <sheet name="構成保護1" sheetId="1" r:id="rId1"/>
@@ -432,7 +432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C928C4-C8BE-4867-A81D-8B74908EA04B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1865B85B-FFBD-4B2F-80BD-E9EB19C1ECA1}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -451,7 +451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84AE7AFC-47DB-4C76-855D-56C3FA4C841F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C5C30E-B483-470F-A741-2A861285ACD2}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
